--- a/test/input/ray/射线检测委托台账.xlsx
+++ b/test/input/ray/射线检测委托台账.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26501"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\code\report-generator\test\input\ray\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54B6820-A5C3-4FDF-AA80-EEEC8ED76EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18468" windowHeight="8700"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="空分质量部抽检" sheetId="5" r:id="rId1"/>
@@ -18,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
   <si>
     <t>委托日期</t>
   </si>
@@ -165,19 +171,25 @@
   </si>
   <si>
     <t>外观检查填写合格</t>
+  </si>
+  <si>
+    <t>发</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>A1</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="34">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,148 +282,24 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -438,7 +326,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.5"/>
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,194 +348,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -670,298 +372,44 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -974,11 +422,11 @@
     <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -988,131 +436,93 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="6" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="11" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="7" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00FF0000"/>
-      <color rgb="00FFFF00"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFF00"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
@@ -1128,13 +538,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2" descr="a955c63e00d9fc5612b324a4c5dab81"/>
+        <xdr:cNvPr id="3" name="图片 2" descr="a955c63e00d9fc5612b324a4c5dab81">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1164,9 +580,15 @@
       <xdr:row>4</xdr:row>
       <xdr:rowOff>159385</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="直接箭头连接符 3"/>
+        <xdr:cNvPr id="4" name="直接箭头连接符 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1211,9 +633,15 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>185420</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="直接箭头连接符 4"/>
+        <xdr:cNvPr id="5" name="直接箭头连接符 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1258,9 +686,15 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>264795</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直接箭头连接符 6"/>
+        <xdr:cNvPr id="7" name="直接箭头连接符 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1305,9 +739,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>254635</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直接箭头连接符 7"/>
+        <xdr:cNvPr id="8" name="直接箭头连接符 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1352,9 +792,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>185420</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="9" name="直接箭头连接符 8"/>
+        <xdr:cNvPr id="9" name="直接箭头连接符 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1399,9 +845,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>46990</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="10" name="直接箭头连接符 9"/>
+        <xdr:cNvPr id="10" name="直接箭头连接符 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1446,9 +898,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>46990</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="11" name="直接箭头连接符 10"/>
+        <xdr:cNvPr id="11" name="直接箭头连接符 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1493,9 +951,15 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="12" name="直接箭头连接符 11"/>
+        <xdr:cNvPr id="12" name="直接箭头连接符 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1540,9 +1004,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>304165</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="13" name="直接箭头连接符 12"/>
+        <xdr:cNvPr id="13" name="直接箭头连接符 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1587,9 +1057,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>205105</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直接箭头连接符 13"/>
+        <xdr:cNvPr id="14" name="直接箭头连接符 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1634,9 +1110,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>36195</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="15" name="直接箭头连接符 14"/>
+        <xdr:cNvPr id="15" name="直接箭头连接符 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1681,9 +1163,15 @@
       <xdr:row>11</xdr:row>
       <xdr:rowOff>36195</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="16" name="直接箭头连接符 15"/>
+        <xdr:cNvPr id="16" name="直接箭头连接符 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -1999,513 +1487,518 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="25" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.62962962962963" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="23" style="3" customWidth="1"/>
-    <col min="4" max="4" width="23.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.62962962962963" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.8796296296296" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.87962962962963" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.87962962962963" style="4" customWidth="1"/>
-    <col min="10" max="10" width="6.22222222222222" style="4" customWidth="1"/>
-    <col min="11" max="11" width="11.5555555555556" style="5" customWidth="1"/>
-    <col min="12" max="12" width="13.2222222222222" style="5" customWidth="1"/>
-    <col min="13" max="13" width="10" style="5" customWidth="1"/>
-    <col min="14" max="14" width="11.7777777777778" style="5" customWidth="1"/>
-    <col min="15" max="15" width="13.8888888888889" style="5" customWidth="1"/>
-    <col min="16" max="16" width="7.77777777777778" style="5" customWidth="1"/>
-    <col min="17" max="17" width="11.1111111111111" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9.44444444444444" style="5" customWidth="1"/>
-    <col min="19" max="19" width="7.66666666666667" style="6" customWidth="1"/>
-    <col min="20" max="20" width="9" style="2"/>
-    <col min="21" max="21" width="16.8888888888889" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9" style="2"/>
+    <col min="3" max="3" width="23" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="12" width="13.25" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="11.75" customWidth="1"/>
+    <col min="15" max="15" width="13.875" customWidth="1"/>
+    <col min="16" max="16" width="7.75" customWidth="1"/>
+    <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="18" max="18" width="9.5" customWidth="1"/>
+    <col min="19" max="19" width="7.625" customWidth="1"/>
+    <col min="21" max="21" width="16.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="33" t="s">
+      <c r="Q1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="34" t="s">
+      <c r="U1" s="30" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="30">
+      <c r="M2" s="26">
         <v>2</v>
       </c>
-      <c r="N2" s="30">
+      <c r="N2" s="26">
         <v>2</v>
       </c>
-      <c r="O2" s="20"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="27"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="31"/>
+      <c r="T2" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" s="23"/>
     </row>
-    <row r="3" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="30">
+      <c r="M3" s="26">
         <v>2</v>
       </c>
-      <c r="N3" s="30">
+      <c r="N3" s="26">
         <v>2</v>
       </c>
-      <c r="O3" s="20"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="27"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="23"/>
     </row>
-    <row r="4" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="26">
         <v>2</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="26">
         <v>2</v>
       </c>
-      <c r="O4" s="20"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="27"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+      <c r="R4" s="23"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="23"/>
     </row>
-    <row r="5" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M5" s="30">
+      <c r="M5" s="26">
         <v>2</v>
       </c>
-      <c r="N5" s="30">
+      <c r="N5" s="26">
         <v>2</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="27"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="23"/>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="H6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="31">
+      <c r="M6" s="27">
         <v>2</v>
       </c>
-      <c r="N6" s="31">
+      <c r="N6" s="27">
         <v>1</v>
       </c>
-      <c r="O6" s="20"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="27"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="23"/>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="27">
         <v>1</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="27">
         <v>1</v>
       </c>
-      <c r="O7" s="20"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="27"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="23"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="15" customHeight="1" spans="1:21">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="27"/>
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="23"/>
     </row>
-    <row r="9" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:21">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="27"/>
+    <row r="9" spans="1:24" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="23"/>
     </row>
-    <row r="10" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:21">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="27"/>
+    <row r="10" spans="1:24" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="23"/>
     </row>
-    <row r="11" s="2" customFormat="1" hidden="1" customHeight="1" spans="1:21">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="27"/>
+    <row r="11" spans="1:24" ht="24.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="23"/>
     </row>
-    <row r="13" customHeight="1" spans="22:22">
+    <row r="13" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="V13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="22:22">
+    <row r="14" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="V14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="6:24">
-      <c r="F15" s="3" t="s">
+    <row r="15" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F15" s="2" t="s">
         <v>45</v>
       </c>
       <c r="V15" t="s">
@@ -2515,21 +2008,20 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="22:22">
+    <row r="16" spans="1:24" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="V16" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S11">
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.511805555555556" right="0.118055555555556" top="0.432638888888889" bottom="0.354166666666667" header="0.156944444444444" footer="0.118055555555556"/>
-  <pageSetup paperSize="9" scale="25" orientation="landscape" horizontalDpi="600"/>
+  <autoFilter ref="A1:S11" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.51180555555555596" right="0.118055555555556" top="0.43263888888888902" bottom="0.35416666666666702" header="0.156944444444444" footer="0.118055555555556"/>
+  <pageSetup paperSize="9" scale="25" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C第 &amp;P 页，共 &amp;N 页</oddHeader>
-    <oddFooter>&amp;L共计：          &amp;C               拍片人：                     废片：                       &amp;R      日期：         </oddFooter>
+    <oddFooter>&amp;L共计：          &amp;C               拍片人：                     废片：                       &amp;R      日期：</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/test/input/ray/射线检测委托台账.xlsx
+++ b/test/input/ray/射线检测委托台账.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\code\report-generator\test\input\ray\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54B6820-A5C3-4FDF-AA80-EEEC8ED76EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F354D7-088B-4A36-A105-290B4C75729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="4335" windowWidth="28800" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="空分质量部抽检" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="53">
   <si>
     <t>委托日期</t>
   </si>
@@ -182,6 +182,10 @@
   </si>
   <si>
     <t>a</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -1634,7 +1638,9 @@
       <c r="R2" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="S2" s="31"/>
+      <c r="S2" s="33" t="s">
+        <v>52</v>
+      </c>
       <c r="T2" s="33" t="s">
         <v>50</v>
       </c>
